--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:26:54+00:00</t>
+    <t>2025-01-23T13:26:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-23T13:26:37+00:00</t>
+    <t>2025-01-24T17:22:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T17:22:23+00:00</t>
+    <t>2025-01-29T14:25:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T14:25:50+00:00</t>
+    <t>2025-01-29T15:50:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T15:50:40+00:00</t>
+    <t>2025-01-30T15:03:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-30T15:03:39+00:00</t>
+    <t>2025-01-31T08:45:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T08:45:39+00:00</t>
+    <t>2025-02-18T10:06:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="148">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T10:06:11+00:00</t>
+    <t>2025-02-18T11:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>representedCustodianOrganization contient les éléments caractérisant la structure conservant le document, à savoir l'identifiant, le nom, les adresses géopostales et de télécommunication.</t>
+    <t>L'élément de l'en-tête du CDA representedCustodianOrganization contient les éléments caractérisant la structure conservant le document, à savoir l'identifiant, le nom, les adresses géopostales et de télécommunication.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -409,6 +409,36 @@
     <t>CustodianOrganization.id</t>
   </si>
   <si>
+    <t>Identifiant de la structure.</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.displayable</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.root</t>
+  </si>
+  <si>
+    <t>- Pour une structure sanitaire ou médico-sociale : valeur fixée à '1.2.250.1.71.4.2.2' 
+- Pour le DMP hébergeant les documents d'expression personnelle du patient ou les documents produits par un système via un SNR : 
+valeur fixée à '1.2.250.1.213.4.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>CustodianOrganization.id.extension</t>
+  </si>
+  <si>
+    <t>- Pour une structure sanitaire ou médico-sociale : valeur de Struct_idNat (voir annexe [6]) 
+- Pour le DMP hébergeant les documents d'expression personnelle du patient ou les documents produits par un système via un SNR : Non renseigné</t>
+  </si>
+  <si>
     <t>CustodianOrganization.name</t>
   </si>
   <si>
@@ -416,6 +446,11 @@
 </t>
   </si>
   <si>
+    <t>Nom de la structure : 
+- Pour une structure sanitaire ou médico-sociale : valeur de Struct_Nom (voir annexe [6]) 
+- Pour le DMP hébergeant les documents d'expression personnelle du patient ou les documents produits par un système via un SNR : valeur fixée à 'DMP'</t>
+  </si>
+  <si>
     <t>CustodianOrganization.telecom</t>
   </si>
   <si>
@@ -423,6 +458,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom de la structure.</t>
+  </si>
+  <si>
     <t>CustodianOrganization.sdtcTelecom</t>
   </si>
   <si>
@@ -431,6 +469,9 @@
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/AD
 </t>
+  </si>
+  <si>
+    <t>Adresse géopostale de la structure.</t>
   </si>
 </sst>
 </file>
@@ -732,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK18"/>
+  <dimension ref="A1:AK23"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.55859375" customWidth="true" bestFit="true"/>
@@ -2130,7 +2171,9 @@
       <c r="K14" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2201,16 +2244,18 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
@@ -2227,10 +2272,12 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="M15" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2256,13 +2303,11 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2280,7 +2325,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>129</v>
+        <v>89</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2309,7 +2354,9 @@
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
       </c>
@@ -2326,10 +2373,12 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
+      <c r="M16" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -2379,7 +2428,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2399,21 +2448,23 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="F17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2425,10 +2476,12 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>132</v>
+        <v>106</v>
       </c>
       <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
+      <c r="M17" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -2478,13 +2531,13 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>74</v>
@@ -2498,16 +2551,18 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="F18" t="s" s="2">
         <v>80</v>
       </c>
@@ -2524,10 +2579,14 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -2577,7 +2636,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2592,6 +2651,513 @@
         <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K19" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF19" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AG19" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH19" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ19" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK19" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E20" s="2"/>
+      <c r="F20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K20" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF20" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AG20" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH20" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ20" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK20" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="B21" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E21" s="2"/>
+      <c r="F21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K21" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>143</v>
+      </c>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q21" s="2"/>
+      <c r="R21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF21" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="AG21" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH21" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ21" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK21" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="B22" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E22" s="2"/>
+      <c r="F22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K22" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="B23" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E23" s="2"/>
+      <c r="F23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K23" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="L23" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF23" t="s" s="2">
+        <v>145</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK23" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T11:00:40+00:00</t>
+    <t>2025-02-18T15:10:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:10:02+00:00</t>
+    <t>2025-02-18T15:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:17:48+00:00</t>
+    <t>2025-02-18T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:09+00:00</t>
+    <t>2025-02-18T15:18:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:18:38+00:00</t>
+    <t>2025-02-18T15:24:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:24:54+00:00</t>
+    <t>2025-02-18T15:28:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:28:32+00:00</t>
+    <t>2025-02-18T15:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:29:38+00:00</t>
+    <t>2025-02-18T15:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:04+00:00</t>
+    <t>2025-02-18T15:30:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:23+00:00</t>
+    <t>2025-02-18T15:30:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-18T15:30:53+00:00</t>
+    <t>2025-02-20T13:34:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:34:17+00:00</t>
+    <t>2025-02-20T13:46:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:46:00+00:00</t>
+    <t>2025-02-20T13:48:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:48:47+00:00</t>
+    <t>2025-02-20T13:50:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:16+00:00</t>
+    <t>2025-02-20T13:50:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:50:51+00:00</t>
+    <t>2025-02-20T13:51:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:51:52+00:00</t>
+    <t>2025-02-20T13:53:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:17+00:00</t>
+    <t>2025-02-20T13:53:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T13:53:53+00:00</t>
+    <t>2025-02-20T14:37:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:37:28+00:00</t>
+    <t>2025-02-20T14:38:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:00+00:00</t>
+    <t>2025-02-20T14:38:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:38:23+00:00</t>
+    <t>2025-02-20T14:42:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:14+00:00</t>
+    <t>2025-02-20T14:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:42:55+00:00</t>
+    <t>2025-02-20T14:43:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:43:30+00:00</t>
+    <t>2025-02-20T14:45:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:45:32+00:00</t>
+    <t>2025-02-20T14:47:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:47:06+00:00</t>
+    <t>2025-02-20T14:48:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:48:16+00:00</t>
+    <t>2025-02-20T15:31:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T15:31:18+00:00</t>
+    <t>2025-02-21T13:12:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T13:12:29+00:00</t>
+    <t>2025-02-21T15:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-21T15:18:09+00:00</t>
+    <t>2025-02-23T14:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-23T14:02:58+00:00</t>
+    <t>2025-02-24T10:33:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T10:33:29+00:00</t>
+    <t>2025-02-24T11:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T11:08:59+00:00</t>
+    <t>2025-02-24T14:08:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
+++ b/HTR-IGDoc/ig/StructureDefinition-fr-core-represented-custodian-organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T14:08:41+00:00</t>
+    <t>2025-02-25T09:00:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
